--- a/integration_test/fixtures/transactions_skip_rows.xlsx
+++ b/integration_test/fixtures/transactions_skip_rows.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">Report generated on 2025-03-01</t>
   </si>
@@ -19,7 +19,10 @@
     <t xml:space="preserve">Account: Checking 12345</t>
   </si>
   <si>
-    <t xml:space="preserve">Date</t>
+    <t xml:space="preserve">Data_Operazione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data_Valuta</t>
   </si>
   <si>
     <t xml:space="preserve">Amount</t>
@@ -300,27 +303,36 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
         <v>45717.0</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="C4" s="3">
         <v>-80.0</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
         <v>45721.0</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
+        <v>45721.0</v>
+      </c>
+      <c r="C5" s="3">
         <v>3000.0</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
